--- a/artfynd/A 63850-2021 artfynd.xlsx
+++ b/artfynd/A 63850-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63850-2021 artfynd.xlsx
+++ b/artfynd/A 63850-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97249244</v>
+        <v>97249165</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590882.3058862248</v>
+        <v>590890</v>
       </c>
       <c r="R2" t="n">
-        <v>6400660.531518416</v>
+        <v>6400596</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,19 +755,9 @@
           <t>2021-11-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,51 +785,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97249208</v>
+        <v>97249301</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590909.5855800156</v>
+        <v>590862</v>
       </c>
       <c r="R3" t="n">
-        <v>6400637.115753445</v>
+        <v>6400650</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,19 +860,9 @@
           <t>2021-11-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,15 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97249165</v>
+        <v>114449814</v>
       </c>
       <c r="B4" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,46 +901,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A63850, Böljerum, Verkebäck, Sm</t>
+          <t>A 63850, Böljerum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590890.1785546211</v>
+        <v>590863</v>
       </c>
       <c r="R4" t="n">
-        <v>6400596.092993968</v>
+        <v>6400689</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,22 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,15 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97249301</v>
+        <v>97249348</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,24 +1010,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1089,14 +1041,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A63850, Böljerum, Verkebäck, Sm</t>
+          <t>A63850, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590861.6664783144</v>
+        <v>590747</v>
       </c>
       <c r="R5" t="n">
-        <v>6400650.454239954</v>
+        <v>6400621</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,19 +1078,9 @@
           <t>2021-11-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,62 +1108,56 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97249279</v>
+        <v>114449752</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A63850, Böljerum, Verkebäck, Sm</t>
+          <t>A 63850, Böljerum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590861.6664783144</v>
+        <v>590946</v>
       </c>
       <c r="R6" t="n">
-        <v>6400650.454239954</v>
+        <v>6400710</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,22 +1184,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,65 +1217,56 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97249227</v>
+        <v>114449339</v>
       </c>
       <c r="B7" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A63850, Böljerum, Verkebäck, Sm</t>
+          <t>A 63850, Böljerum, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590909.5855800156</v>
+        <v>590837</v>
       </c>
       <c r="R7" t="n">
-        <v>6400637.115753445</v>
+        <v>6400563</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1373,22 +1290,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bearbetat granstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,65 +1327,60 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114424353</v>
+        <v>97249227</v>
       </c>
       <c r="B8" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 63850, Böljerum, Sm</t>
+          <t>A63850, Böljerum, Verkebäck, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590772</v>
+        <v>590910</v>
       </c>
       <c r="R8" t="n">
-        <v>6400625</v>
+        <v>6400637</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1497,12 +1404,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,7 +1418,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1530,51 +1436,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114424482</v>
+        <v>114449783</v>
       </c>
       <c r="B9" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1582,13 +1483,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590792</v>
+        <v>590946</v>
       </c>
       <c r="R9" t="n">
-        <v>6400600</v>
+        <v>6400710</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1612,12 +1513,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,7 +1527,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1645,15 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114449498</v>
+        <v>97249208</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1575,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1693,14 +1588,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 63850, Böljerum, Sm</t>
+          <t>A63850, Böljerum, Verkebäck, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590931</v>
+        <v>590910</v>
       </c>
       <c r="R10" t="n">
-        <v>6400592</v>
+        <v>6400637</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1727,12 +1622,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,15 +1655,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114449884</v>
+        <v>97249244</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,11 +1683,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1808,14 +1694,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 63850, Böljerum, Sm</t>
+          <t>A63850, Böljerum, Verkebäck, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590853</v>
+        <v>590882</v>
       </c>
       <c r="R11" t="n">
-        <v>6400677</v>
+        <v>6400661</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,12 +1728,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1875,15 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114449570</v>
+        <v>97249279</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1791,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1923,14 +1804,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 63850, Böljerum, Sm</t>
+          <t>A63850, Böljerum, Verkebäck, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590936</v>
+        <v>590862</v>
       </c>
       <c r="R12" t="n">
-        <v>6400635</v>
+        <v>6400650</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1957,12 +1838,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1990,50 +1871,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114449752</v>
+        <v>114449414</v>
       </c>
       <c r="B13" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2041,10 +1918,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590946</v>
+        <v>590887</v>
       </c>
       <c r="R13" t="n">
-        <v>6400710</v>
+        <v>6400608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2104,15 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114449604</v>
+        <v>114449484</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2011,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2156,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590946</v>
+        <v>590906</v>
       </c>
       <c r="R14" t="n">
-        <v>6400665</v>
+        <v>6400620</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2219,40 +2091,39 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114449393</v>
+        <v>114449498</v>
       </c>
       <c r="B15" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2267,10 +2138,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590868</v>
+        <v>590931</v>
       </c>
       <c r="R15" t="n">
-        <v>6400607</v>
+        <v>6400592</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2330,15 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114449633</v>
+        <v>114449505</v>
       </c>
       <c r="B16" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2231,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2382,10 +2248,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590959</v>
+        <v>590923</v>
       </c>
       <c r="R16" t="n">
-        <v>6400666</v>
+        <v>6400608</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2445,15 +2311,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114449688</v>
+        <v>114449539</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2341,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2497,10 +2358,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590945</v>
+        <v>590916</v>
       </c>
       <c r="R17" t="n">
-        <v>6400668</v>
+        <v>6400597</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2563,12 +2424,7 @@
         <v>114449553</v>
       </c>
       <c r="B18" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2675,15 +2531,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114449587</v>
+        <v>114449570</v>
       </c>
       <c r="B19" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2561,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2727,10 +2578,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590927</v>
+        <v>590936</v>
       </c>
       <c r="R19" t="n">
-        <v>6400634</v>
+        <v>6400635</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2790,15 +2641,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114449505</v>
+        <v>114449581</v>
       </c>
       <c r="B20" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,7 +2671,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2842,10 +2688,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590923</v>
+        <v>590943</v>
       </c>
       <c r="R20" t="n">
-        <v>6400608</v>
+        <v>6400633</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2905,15 +2751,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114449841</v>
+        <v>114449587</v>
       </c>
       <c r="B21" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2940,7 +2781,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2957,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590868</v>
+        <v>590927</v>
       </c>
       <c r="R21" t="n">
-        <v>6400700</v>
+        <v>6400634</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3020,15 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>114449484</v>
+        <v>114449604</v>
       </c>
       <c r="B22" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +2891,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3072,10 +2908,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590906</v>
+        <v>590946</v>
       </c>
       <c r="R22" t="n">
-        <v>6400620</v>
+        <v>6400665</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3135,15 +2971,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>114449414</v>
+        <v>114449633</v>
       </c>
       <c r="B23" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3170,7 +3001,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3187,10 +3018,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590887</v>
+        <v>590959</v>
       </c>
       <c r="R23" t="n">
-        <v>6400608</v>
+        <v>6400666</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3250,15 +3081,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>114449713</v>
+        <v>114449661</v>
       </c>
       <c r="B24" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3285,7 +3111,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3305,7 +3131,7 @@
         <v>590949</v>
       </c>
       <c r="R24" t="n">
-        <v>6400670</v>
+        <v>6400665</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3365,15 +3191,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>114449539</v>
+        <v>114449688</v>
       </c>
       <c r="B25" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3400,7 +3221,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3417,10 +3238,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590916</v>
+        <v>590945</v>
       </c>
       <c r="R25" t="n">
-        <v>6400597</v>
+        <v>6400668</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3480,50 +3301,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>114449814</v>
+        <v>114449713</v>
       </c>
       <c r="B26" t="n">
-        <v>90735</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3531,10 +3348,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590863</v>
+        <v>590949</v>
       </c>
       <c r="R26" t="n">
-        <v>6400689</v>
+        <v>6400670</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3594,15 +3411,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>114449661</v>
+        <v>114449841</v>
       </c>
       <c r="B27" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3629,7 +3441,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3646,10 +3458,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>590949</v>
+        <v>590868</v>
       </c>
       <c r="R27" t="n">
-        <v>6400665</v>
+        <v>6400700</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3709,15 +3521,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>114449581</v>
+        <v>114449884</v>
       </c>
       <c r="B28" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3744,7 +3551,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3761,10 +3568,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>590943</v>
+        <v>590853</v>
       </c>
       <c r="R28" t="n">
-        <v>6400633</v>
+        <v>6400677</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3824,51 +3631,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>114449783</v>
+        <v>114424353</v>
       </c>
       <c r="B29" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3876,13 +3678,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>590946</v>
+        <v>590772</v>
       </c>
       <c r="R29" t="n">
-        <v>6400710</v>
+        <v>6400625</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3906,12 +3708,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3920,6 +3722,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3935,6 +3738,222 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>114424482</v>
+      </c>
+      <c r="B30" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>A 63850, Böljerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>590792</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6400600</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-01-27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-01-27</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>114449393</v>
+      </c>
+      <c r="B31" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>A 63850, Böljerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>590868</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6400607</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
